--- a/Files/kalyan-penal-chart.xlsx
+++ b/Files/kalyan-penal-chart.xlsx
@@ -10,7 +10,7 @@
     <x:sheet name="Source" sheetId="2" r:id="rId3"/>
   </x:sheets>
   <x:definedNames>
-    <x:definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">Data!$A$1:$V$701</x:definedName>
+    <x:definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">Data!$A$1:$V$702</x:definedName>
   </x:definedNames>
   <x:calcPr calcId="125725"/>
 </x:workbook>
@@ -3610,7 +3610,7 @@
   <x:sheetPr>
     <x:outlinePr summaryBelow="1" summaryRight="1"/>
   </x:sheetPr>
-  <x:dimension ref="A1:V701"/>
+  <x:dimension ref="A1:V702"/>
   <x:sheetFormatPr defaultRowHeight="15"/>
   <x:cols>
     <x:col min="1" max="1" width="28.710625" style="0" customWidth="1"/>
@@ -51240,40 +51240,40 @@
         <x:v>194</x:v>
       </x:c>
       <x:c r="H701" s="3" t="s">
-        <x:v>41</x:v>
+        <x:v>165</x:v>
       </x:c>
       <x:c r="I701" s="3" t="s">
-        <x:v>41</x:v>
+        <x:v>50</x:v>
       </x:c>
       <x:c r="J701" s="3" t="s">
-        <x:v>41</x:v>
+        <x:v>120</x:v>
       </x:c>
       <x:c r="K701" s="3" t="s">
-        <x:v>41</x:v>
+        <x:v>46</x:v>
       </x:c>
       <x:c r="L701" s="3" t="s">
-        <x:v>41</x:v>
+        <x:v>168</x:v>
       </x:c>
       <x:c r="M701" s="3" t="s">
-        <x:v>41</x:v>
+        <x:v>26</x:v>
       </x:c>
       <x:c r="N701" s="3" t="s">
-        <x:v>41</x:v>
+        <x:v>165</x:v>
       </x:c>
       <x:c r="O701" s="3" t="s">
-        <x:v>41</x:v>
+        <x:v>89</x:v>
       </x:c>
       <x:c r="P701" s="3" t="s">
-        <x:v>41</x:v>
+        <x:v>69</x:v>
       </x:c>
       <x:c r="Q701" s="3" t="s">
-        <x:v>41</x:v>
+        <x:v>153</x:v>
       </x:c>
       <x:c r="R701" s="3" t="s">
-        <x:v>41</x:v>
+        <x:v>30</x:v>
       </x:c>
       <x:c r="S701" s="3" t="s">
-        <x:v>41</x:v>
+        <x:v>96</x:v>
       </x:c>
       <x:c r="T701" s="3" t="s">
         <x:v>41</x:v>
@@ -51285,8 +51285,76 @@
         <x:v>41</x:v>
       </x:c>
     </x:row>
+    <x:row r="702" spans="1:22">
+      <x:c r="A702" s="3" t="s">
+        <x:v>1045</x:v>
+      </x:c>
+      <x:c r="B702" s="3" t="s">
+        <x:v>160</x:v>
+      </x:c>
+      <x:c r="C702" s="3" t="s">
+        <x:v>250</x:v>
+      </x:c>
+      <x:c r="D702" s="3" t="s">
+        <x:v>28</x:v>
+      </x:c>
+      <x:c r="E702" s="3" t="s">
+        <x:v>41</x:v>
+      </x:c>
+      <x:c r="F702" s="3" t="s">
+        <x:v>41</x:v>
+      </x:c>
+      <x:c r="G702" s="3" t="s">
+        <x:v>41</x:v>
+      </x:c>
+      <x:c r="H702" s="3" t="s">
+        <x:v>41</x:v>
+      </x:c>
+      <x:c r="I702" s="3" t="s">
+        <x:v>41</x:v>
+      </x:c>
+      <x:c r="J702" s="3" t="s">
+        <x:v>41</x:v>
+      </x:c>
+      <x:c r="K702" s="3" t="s">
+        <x:v>41</x:v>
+      </x:c>
+      <x:c r="L702" s="3" t="s">
+        <x:v>41</x:v>
+      </x:c>
+      <x:c r="M702" s="3" t="s">
+        <x:v>41</x:v>
+      </x:c>
+      <x:c r="N702" s="3" t="s">
+        <x:v>41</x:v>
+      </x:c>
+      <x:c r="O702" s="3" t="s">
+        <x:v>41</x:v>
+      </x:c>
+      <x:c r="P702" s="3" t="s">
+        <x:v>41</x:v>
+      </x:c>
+      <x:c r="Q702" s="3" t="s">
+        <x:v>41</x:v>
+      </x:c>
+      <x:c r="R702" s="3" t="s">
+        <x:v>41</x:v>
+      </x:c>
+      <x:c r="S702" s="3" t="s">
+        <x:v>41</x:v>
+      </x:c>
+      <x:c r="T702" s="3" t="s">
+        <x:v>41</x:v>
+      </x:c>
+      <x:c r="U702" s="3" t="s">
+        <x:v>41</x:v>
+      </x:c>
+      <x:c r="V702" s="3" t="s">
+        <x:v>41</x:v>
+      </x:c>
+    </x:row>
   </x:sheetData>
-  <x:autoFilter ref="A1:V701"/>
+  <x:autoFilter ref="A1:V702"/>
   <x:printOptions horizontalCentered="0" verticalCentered="0" headings="0" gridLines="0"/>
   <x:pageMargins left="0.75" right="0.75" top="0.75" bottom="0.5" header="0.5" footer="0.75"/>
   <x:pageSetup paperSize="1" scale="100" pageOrder="downThenOver" orientation="default" blackAndWhite="0" draft="0" cellComments="none" errors="displayed"/>
@@ -51336,7 +51404,7 @@
         <x:v>1052</x:v>
       </x:c>
       <x:c r="B4" s="6">
-        <x:v>700</x:v>
+        <x:v>701</x:v>
       </x:c>
     </x:row>
     <x:row r="5" spans="1:2">
